--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_tarapaca.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_tarapaca.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:40</t>
+    <t xml:space="preserve">2026-09-09 20:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_tarapaca.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_tarapaca.xlsx
@@ -24,6 +24,9 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Iquique</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto Hospicio</t>
   </si>
   <si>
@@ -33,9 +36,6 @@
     <t xml:space="preserve">Huara</t>
   </si>
   <si>
-    <t xml:space="preserve">Iquique</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pica</t>
   </si>
   <si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:44</t>
+    <t xml:space="preserve">2026-09-18 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.09</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.75</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.67</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
